--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67607_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67607_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R67cb9aba5d824c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re17fba64a053480e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67607_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_67607_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re17fba64a053480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R12dca5407b624725"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,58 +984,928 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      1.4898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2955</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4898</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7684</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      1.8184</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8184</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/08/2026</x:t>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -330,52 +1920,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/08/2026</x:t>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -390,7 +1950,52 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>14/08/2026</x:t>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -405,7 +2010,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/08/2026</x:t>
+          <x:t>15/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -420,22 +2025,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
+          <x:t>14/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -450,7 +2040,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>10/08/2026</x:t>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -465,82 +2070,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.1436</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0863</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
+          <x:t>11/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -555,22 +2085,127 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.4498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2621</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2621</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5151</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -585,52 +2220,37 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.5819</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -645,7 +2265,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>28/07/2026</x:t>
+          <x:t>29/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -660,7 +2280,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>27/07/2026</x:t>
+          <x:t>28/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -675,7 +2295,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>26/07/2026</x:t>
+          <x:t>27/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -690,67 +2310,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
+          <x:t>26/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -765,802 +2325,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.2022</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5794</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4914</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6250</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6717</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8184</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7684</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9220</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8184</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0303</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9220</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0303</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.1436</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0863</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.2621</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.2621</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3858</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.5151</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7198</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.5819</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.6501</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7910</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8637</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8637</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
+          <x:t>25/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1575,51 +2340,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8637</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.9379</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>24/05/2026</x:t>
         </x:is>
       </x:c>
@@ -2064,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9583</x:v>
+        <x:v>      9.2806</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9583</x:v>
+        <x:v>      9.2806</x:v>
       </x:c>
     </x:row>
     <x:row>
